--- a/Optim/tech_locations.xlsx
+++ b/Optim/tech_locations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanhachez/Library/CloudStorage/OneDrive-VrijeUniversiteitBrussel/Publications/Articles/ongoing - DHCN-RBC/Code/DHNRBC/Optim/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\local-admin\Documents\CODE\DHNRBC\Optim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B2E5156-2358-5F4A-A062-F19F5788AF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD66676A-F08D-4F1F-913F-6E8555E937C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1880" yWindow="7440" windowWidth="30240" windowHeight="17600" xr2:uid="{E4991306-0B28-E847-84A0-269833AD7A05}"/>
+    <workbookView xWindow="4935" yWindow="-16125" windowWidth="21600" windowHeight="12645" activeTab="1" xr2:uid="{E4991306-0B28-E847-84A0-269833AD7A05}"/>
   </bookViews>
   <sheets>
     <sheet name="building_access" sheetId="1" r:id="rId1"/>
@@ -192,7 +192,7 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -201,16 +201,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF6A9955"/>
-      <name val="Menlo"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF6A9955"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -233,16 +240,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -260,12 +270,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -562,309 +568,312 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2142ABB-39FF-024F-92E0-A48853967801}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="52.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="52.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2">
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>2332</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="3">
         <v>21.2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3">
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2">
         <v>40</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>6512</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="3">
         <v>59.2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4">
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2">
         <v>5</v>
       </c>
-      <c r="F4">
+      <c r="E4" s="2"/>
+      <c r="F4" s="2">
         <v>52</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="3">
         <v>0.47272727272727277</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5">
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2">
         <v>15</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>6660</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="3">
         <v>60.545454545454547</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6">
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>1680</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="3">
         <v>15.272727272727272</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7">
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2">
         <v>5</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>391</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="3">
         <v>3.5545454545454547</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>20</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="2">
         <v>2741</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="3">
         <v>31.69863945578232</v>
       </c>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>2</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="2">
         <v>344</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="3">
         <v>3.9782312925170067</v>
       </c>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>100</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="2">
         <v>33520</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="3">
         <v>387.64625850340138</v>
       </c>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
         <v>10</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="2">
         <v>3794</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="3">
         <v>43.87619047619048</v>
       </c>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="2">
         <v>40</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="2">
         <v>6924</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="3">
         <v>80.073469387755097</v>
       </c>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13">
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2">
         <v>23</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="2" t="s">
         <v>34</v>
       </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -875,335 +884,337 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE867C69-2820-DF4A-A402-9FC87B6EA813}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" customWidth="1"/>
-    <col min="5" max="5" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="22.33203125" customWidth="1"/>
-    <col min="9" max="9" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="11" style="4"/>
+    <col min="3" max="3" width="18.875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="22.375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="29.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="22.375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="28.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="11" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
         <v>17</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="6">
         <v>1.1599999999999999</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="4">
         <v>0.84</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="4">
         <v>0.15</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="7">
         <f>45193/E2</f>
         <v>53801.190476190481</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="7">
         <f>0.64/E2</f>
         <v>0.76190476190476197</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="5">
         <f>24.68/F3*E3</f>
         <v>58.72137931034483</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="9">
         <f>3.28*F3/E3</f>
         <v>1.3785507246376809</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="4">
         <v>0.69</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="4">
         <v>0.28999999999999998</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="7">
         <f>42000/E3</f>
         <v>60869.565217391311</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="7">
         <f>0.61/E3</f>
         <v>0.88405797101449279</v>
       </c>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="I3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>554.4</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="9">
         <v>1.17</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="4">
         <v>0.66</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="4">
         <v>0.3</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="7">
         <f>22765/E4</f>
         <v>34492.42424242424</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="7">
         <f>0.57/E4</f>
         <v>0.86363636363636354</v>
       </c>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="I4" s="8"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="4">
+      <c r="B5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5">
         <v>1</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="4">
         <v>1.1499999999999999</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="4">
         <v>2.75</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="4">
         <v>0</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="7">
         <v>2127</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="7">
         <v>0.86</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="4">
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5">
         <v>3</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="4">
         <v>2.8</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="4">
         <v>0</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="7">
         <v>2127</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="7">
         <v>0.86</v>
       </c>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="I6" s="8"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="4">
+      <c r="B7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
         <v>10</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="4">
         <v>1.02</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="4">
         <v>2.8</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="4">
         <v>0</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="7">
         <v>2127</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="7">
         <v>0.86</v>
       </c>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="I7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="4">
+      <c r="B8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
         <v>0.1</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="4">
         <v>1.93</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="4">
         <v>3.15</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="4">
         <v>0</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="7">
         <v>11000</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="7">
         <v>0</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="4">
+      <c r="B9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
         <v>20</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="4">
         <v>1.1299999999999999</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="4">
         <v>3.2</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="4">
         <v>0</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="7">
         <v>4253</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="7">
         <v>1.27</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="4">
+      <c r="B10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
         <v>1</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="4">
         <v>2.1</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="4">
         <v>4</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="4">
         <v>0</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="7">
         <v>4000</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="7">
         <v>0</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11">
+      <c r="B11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="4">
         <v>1</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="4">
         <v>1.1299999999999999</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="4">
         <v>3.1</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="4">
         <v>0</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="7">
         <v>2127</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="7">
         <v>3.07</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="8" t="s">
         <v>42</v>
       </c>
     </row>
